--- a/data/trans_orig/IP07C09-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C09-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar de todos sus amigos en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24773</t>
+          <t>24605</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26523</t>
+          <t>26470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33224</t>
+          <t>33425</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48409</t>
+          <t>48733</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>55,06%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28178</t>
+          <t>27814</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13875</t>
+          <t>14125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24509</t>
+          <t>24771</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34509</t>
+          <t>33916</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50469</t>
+          <t>49619</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10047</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72185</t>
+          <t>72490</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94598</t>
+          <t>94448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84681</t>
+          <t>85049</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109627</t>
+          <t>107648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>163532</t>
+          <t>164316</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195354</t>
+          <t>196961</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,56%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82940</t>
+          <t>82730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105282</t>
+          <t>105374</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86130</t>
+          <t>86980</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109679</t>
+          <t>111277</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>175889</t>
+          <t>175722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>208631</t>
+          <t>207417</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,13%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17962</t>
+          <t>17915</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14715</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28120</t>
+          <t>27737</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24760</t>
+          <t>24507</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41978</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16535</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28766</t>
+          <t>28118</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13952</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24832</t>
+          <t>24510</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>33827</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49532</t>
+          <t>49398</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>16789</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28420</t>
+          <t>28659</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19613</t>
+          <t>19880</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30884</t>
+          <t>31334</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39167</t>
+          <t>38697</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56408</t>
+          <t>55772</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>13627</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17968</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>112389</t>
+          <t>112035</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>138787</t>
+          <t>138598</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>123651</t>
+          <t>122870</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>149810</t>
+          <t>149748</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>241035</t>
+          <t>240837</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>281190</t>
+          <t>280067</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,88%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124994</t>
+          <t>125639</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>152734</t>
+          <t>153669</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127681</t>
+          <t>129111</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>155918</t>
+          <t>156832</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>261406</t>
+          <t>264766</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>299855</t>
+          <t>303881</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30136</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>19792</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>35501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>40174</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>61561</t>
+          <t>61424</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar de todos sus amigos en 2012 (tasa de respuesta: 95,1%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2012 (tasa de respuesta: 95,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20808</t>
+          <t>21568</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32861</t>
+          <t>33366</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17197</t>
+          <t>15967</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27489</t>
+          <t>27676</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40418</t>
+          <t>41427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56763</t>
+          <t>58014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,94%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24680</t>
+          <t>23918</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11382</t>
+          <t>11286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21931</t>
+          <t>22557</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26751</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>10839</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>16493</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87285</t>
+          <t>87410</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109773</t>
+          <t>110606</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>115854</t>
+          <t>115053</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139541</t>
+          <t>138899</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>208038</t>
+          <t>209389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>243522</t>
+          <t>241821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,33%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69693</t>
+          <t>69658</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92116</t>
+          <t>93329</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65425</t>
+          <t>64675</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89025</t>
+          <t>87465</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140552</t>
+          <t>141233</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>174066</t>
+          <t>174210</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22833</t>
+          <t>22200</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18921</t>
+          <t>19830</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20441</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36892</t>
+          <t>37407</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9498</t>
+          <t>9533</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32208</t>
+          <t>31837</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44501</t>
+          <t>43986</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24727</t>
+          <t>25781</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36908</t>
+          <t>37631</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60746</t>
+          <t>60433</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77630</t>
+          <t>78800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>68,45%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21857</t>
+          <t>21678</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13626</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25246</t>
+          <t>24955</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27361</t>
+          <t>27163</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44531</t>
+          <t>43742</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,0%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14266</t>
+          <t>13596</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>146711</t>
+          <t>149445</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>176647</t>
+          <t>179201</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165415</t>
+          <t>166109</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>196914</t>
+          <t>194846</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>323956</t>
+          <t>324900</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>365437</t>
+          <t>366658</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,86%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>101920</t>
+          <t>100128</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>130336</t>
+          <t>127750</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>98940</t>
+          <t>97458</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>125690</t>
+          <t>126446</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>207592</t>
+          <t>207175</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>246931</t>
+          <t>244762</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>33132</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30668</t>
+          <t>30337</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>37379</t>
+          <t>36830</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>58702</t>
+          <t>58757</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar de todos sus amigos en 2016 (tasa de respuesta: 95,28%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2016 (tasa de respuesta: 95,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15292</t>
+          <t>15235</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>11907</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>22142</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21187</t>
+          <t>21205</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34720</t>
+          <t>34608</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,47%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>18740</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22720</t>
+          <t>22494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24961</t>
+          <t>24354</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38701</t>
+          <t>38708</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,56%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134131</t>
+          <t>133839</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>159973</t>
+          <t>160721</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124575</t>
+          <t>122866</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149119</t>
+          <t>147629</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>264355</t>
+          <t>262830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>300825</t>
+          <t>299947</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,77%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60548</t>
+          <t>61527</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84837</t>
+          <t>84951</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61316</t>
+          <t>61624</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84490</t>
+          <t>85681</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128531</t>
+          <t>129796</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>161770</t>
+          <t>163374</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>15521</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29848</t>
+          <t>30852</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29872</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>33185</t>
+          <t>32293</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55328</t>
+          <t>53799</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>761</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6396</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39053</t>
+          <t>38980</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52241</t>
+          <t>52620</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47326</t>
+          <t>46387</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59934</t>
+          <t>60353</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92137</t>
+          <t>90626</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109501</t>
+          <t>108768</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13510</t>
+          <t>13573</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26566</t>
+          <t>26350</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10031</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21395</t>
+          <t>22471</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26835</t>
+          <t>26555</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42969</t>
+          <t>43385</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>15411</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>188591</t>
+          <t>188942</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>219781</t>
+          <t>219907</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>192969</t>
+          <t>192035</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>221476</t>
+          <t>221772</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>389288</t>
+          <t>390803</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>434426</t>
+          <t>434316</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,79%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93190</t>
+          <t>91155</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121084</t>
+          <t>121751</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>90945</t>
+          <t>91284</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>119181</t>
+          <t>120261</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>190006</t>
+          <t>191305</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>230938</t>
+          <t>231753</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21476</t>
+          <t>21560</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>38650</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>20120</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>36633</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45268</t>
+          <t>46098</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>70496</t>
+          <t>70166</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C09-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C09-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el/la menor en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21114</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15906</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26048</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>48,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>60,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>19270</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13810</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24605</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14278</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>24717</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>42,55%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,5%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>54,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>21114</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>16124</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>26470</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>48,85%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33425</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48733</t>
+          <t>47768</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>53,97%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19393</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14374</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24791</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>44,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>33,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>57,36%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22714</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17032</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27814</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17457</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>28328</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>50,16%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>37,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>61,42%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19393</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14125</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24771</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>44,87%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33916</t>
+          <t>35450</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49619</t>
+          <t>49666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,11%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5048</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,68%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3301</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1289</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7301</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1311</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7339</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>7,29%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5609</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -1061,107 +1061,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3430</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>680</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4885</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4326</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3371</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>45285</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>45285</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>45285</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>96274</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>84365</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>108440</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>44,73%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>50,38%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>83634</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>72490</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>94448</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>73010</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>94799</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>43,93%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>96274</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>85049</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>107648</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>44,73%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164316</t>
+          <t>164161</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196961</t>
+          <t>197691</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>98046</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>85460</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>110252</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>45,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>93926</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>82730</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>105374</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>82475</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>105200</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>49,33%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>43,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>55,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>98046</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>86980</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>111277</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>45,55%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>175722</t>
+          <t>175377</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>207417</t>
+          <t>208601</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,43%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20934</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14464</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>29199</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,73%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,72%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,56%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11523</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6885</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17915</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6844</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>16849</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>6,05%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>20934</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>14715</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27737</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24507</t>
+          <t>24285</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42105</t>
+          <t>42473</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -1743,107 +1743,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1303</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4556</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,68%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4566</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>215254</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>215254</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>215254</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>190386</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>190386</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>190386</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>215254</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>215254</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>215254</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18875</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13526</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>24885</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>50,74%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>22227</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>16535</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>28118</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>16698</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>28343</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>40,98%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>51,83%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>18875</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>13302</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>24510</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>38,49%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33827</t>
+          <t>33172</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49398</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,33%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25451</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>19699</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>30817</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>51,9%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>40,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>62,84%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>22531</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16789</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>28659</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17016</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>29016</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>41,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>30,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>52,83%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>25451</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>19880</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>31334</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>51,9%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38697</t>
+          <t>39678</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55772</t>
+          <t>56011</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,23%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3906</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1667</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7730</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>15,76%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>8108</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>4375</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>13627</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>4245</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>13211</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>14,95%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>25,12%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3906</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1397</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>8135</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3594</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1379</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4810</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4790</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2,54%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,87%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>808</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4177</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>136262</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>122530</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>150785</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>44,31%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>39,84%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>49,03%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>125131</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>112035</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>138598</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>112207</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>139499</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>43,16%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>38,64%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>47,81%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>136262</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>122870</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>149748</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>44,31%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>240837</t>
+          <t>241068</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>280067</t>
+          <t>280178</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,9%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>142890</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>129134</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>158663</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>46,47%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>41,99%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>51,59%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>139170</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>125639</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>153669</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>123787</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>153390</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>48,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>43,34%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>53,0%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>142890</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>129111</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>156832</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>46,47%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>264766</t>
+          <t>263215</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>303881</t>
+          <t>301797</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,52%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>26878</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>19680</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>36064</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>11,73%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>22932</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>16542</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>31882</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>16318</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>30869</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>7,91%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>26878</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>19792</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>35501</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>40174</t>
+          <t>39087</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>61424</t>
+          <t>61517</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -3107,72 +3107,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1488</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2682</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7063</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6751</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1488</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4729</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>8793</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>307518</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>307518</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>307518</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>431</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>289916</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>289916</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>289916</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>307518</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>307518</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>307518</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2012 (tasa de respuesta: 95,1%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el/la menor en 2012 (tasa de respuesta: 95,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22173</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16607</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27960</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>49,1%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,77%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>26970</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21568</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33366</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>21141</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>32960</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>52,24%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>41,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>22173</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>15967</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>27676</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>49,1%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41427</t>
+          <t>40166</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58014</t>
+          <t>57276</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16493</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10932</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22130</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,21%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18011</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12434</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23918</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12398</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24093</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>34,89%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,09%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16493</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11286</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22557</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,52%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>27398</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>43307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,74%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2683</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11197</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12,94%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>24,79%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4612</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1474</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9050</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1782</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9077</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>8,93%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,53%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2761</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10839</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -4020,72 +4020,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2710</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1265</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4275</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3937</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3357</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -4133,107 +4133,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3873</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4275</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>8,28%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4109</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3544</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>127790</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>115558</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>139310</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>57,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>51,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>62,51%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>98184</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>87410</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>110606</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>86950</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>109687</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>49,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>127790</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>115053</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>138899</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>57,34%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>209389</t>
+          <t>208474</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>241821</t>
+          <t>242954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>76290</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>65096</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>87700</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,23%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,35%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>81350</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>69658</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>93329</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>69700</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>92011</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,89%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>35,01%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>76290</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>64675</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>87465</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>34,23%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141233</t>
+          <t>142085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>174210</t>
+          <t>174772</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,43%</t>
         </is>
       </c>
     </row>
@@ -4589,74 +4589,74 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12902</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7885</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19696</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,84%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>15334</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9797</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>22200</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10090</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>22205</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>7,71%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>11,16%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12902</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7953</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>19830</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,79%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>8,9%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>42</t>
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20632</t>
+          <t>20626</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37407</t>
+          <t>36586</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -4702,72 +4702,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3120</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7640</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5699</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5390</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3120</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7553</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -4815,72 +4815,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6876</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2079</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6134</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5627</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2771</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6816</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9533</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>222873</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>222873</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>222873</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>198957</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>198957</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>198957</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>222873</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>222873</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>222873</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>31578</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>25290</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>37217</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>57,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>45,94%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>38096</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>31837</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>43986</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>31655</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>43706</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>63,43%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>53,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>73,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>31578</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>25781</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>37631</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>57,36%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60433</t>
+          <t>60905</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78800</t>
+          <t>78671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,34%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19212</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>26122</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>34,9%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,62%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>47,45%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>15827</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>10913</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>21678</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>10780</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>22213</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>26,35%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>18,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>36,09%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>19212</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>14037</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>24955</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>34,9%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27163</t>
+          <t>27506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43742</t>
+          <t>43884</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3639</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8146</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,61%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14,8%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>4491</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9037</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1892</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>9185</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,48%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3639</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1393</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7828</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,61%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13596</t>
+          <t>14380</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -5497,72 +5497,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2991</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1651</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5551</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5624</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2,75%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2574</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>55054</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>55054</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>55054</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>60065</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>60065</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>60065</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>55054</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>55054</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>55054</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>181540</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>166951</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>196644</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>56,19%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>51,67%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>60,86%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>163250</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>149445</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>179201</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>148770</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>176827</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>52,55%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>48,11%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>57,69%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>181540</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>166109</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>194846</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>56,19%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>324900</t>
+          <t>326330</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>366658</t>
+          <t>366328</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>111994</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>98060</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>127229</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>34,66%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>30,35%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>39,38%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>115188</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>100128</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>127750</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>100891</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>129914</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>37,08%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>32,23%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>41,12%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>111994</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>97458</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>126446</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>34,66%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>207175</t>
+          <t>207712</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>244762</t>
+          <t>245072</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>22387</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>15329</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>30722</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,51%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>24436</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>17531</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>33132</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>17110</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>32379</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>7,87%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>22387</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>15998</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>30337</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36830</t>
+          <t>36863</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>58757</t>
+          <t>59473</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -6066,72 +6066,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7069</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>3275</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1239</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7136</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1246</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>7292</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3771</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>7714</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -6179,72 +6179,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>7608</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>4498</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>1885</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>9777</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>9334</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3396</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>7416</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>323089</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>323089</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>323089</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>442</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>310647</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>310647</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>310647</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>323089</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>323089</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>323089</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2016 (tasa de respuesta: 95,28%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el/la menor en 2016 (tasa de respuesta: 95,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6640,72 +6640,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16964</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11883</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21847</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>46,3%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>32,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>59,63%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10756</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6710</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15235</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6672</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15449</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>35,14%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>16964</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11907</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>22142</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>46,3%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>21175</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34608</t>
+          <t>34357</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,09%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17566</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12718</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22560</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,95%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>34,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>61,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14216</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9657</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18740</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9694</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>18539</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>46,45%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,55%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>61,23%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17566</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12524</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22494</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>47,95%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24354</t>
+          <t>25067</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38708</t>
+          <t>38860</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,79%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1391</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4770</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13,02%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3700</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1396</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8104</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7969</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>12,09%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>26,48%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1391</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4782</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -6984,102 +6984,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3885</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>564</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2774</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2934</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,84%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,59%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3384</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4543</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1281</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4518</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -7092,107 +7092,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1370</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4733</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4592</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>4,48%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4372</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>5116</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>136181</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>124060</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>147778</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,07%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52,9%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>63,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>147336</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>133839</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>160721</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>134077</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>159794</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>60,54%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>55,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>66,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>136181</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>122866</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>147629</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>58,07%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>262830</t>
+          <t>267228</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>299947</t>
+          <t>303203</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>63,45%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>72805</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>60990</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>84187</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,01%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>35,9%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>72240</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>61527</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>84951</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>61031</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>84664</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>29,68%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25,28%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>34,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>72805</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61624</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>85681</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>31,05%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129796</t>
+          <t>126913</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>163374</t>
+          <t>161594</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20560</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14113</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28448</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12,13%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>21591</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>15521</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>30852</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>15421</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>30952</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>8,87%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,68%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>20560</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>14074</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>28916</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32293</t>
+          <t>31799</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53799</t>
+          <t>53818</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -7661,72 +7661,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3015</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7031</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1564</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5377</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4762</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3015</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>761</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7295</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9839</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -7774,72 +7774,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1942</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5578</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>626</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3921</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3603</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5671</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>234504</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>234504</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>234504</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>348</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>243358</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>243358</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>243358</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>234504</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>234504</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>234504</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>54144</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>46628</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>60745</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>71,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>80,45%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>46143</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>38980</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>52620</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>39355</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>53162</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>64,91%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>54,83%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>74,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>54144</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>46387</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>60353</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>71,71%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90626</t>
+          <t>90969</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108768</t>
+          <t>109507</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,7%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14879</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9801</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>21267</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>19,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28,17%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>19697</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13573</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26350</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>13775</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>25910</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>27,71%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19,09%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,07%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>14879</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>10031</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>22471</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>19,71%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26555</t>
+          <t>26799</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43385</t>
+          <t>43598</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,74%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5930</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2811</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11369</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>15,06%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>3772</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7954</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8045</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,31%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>5930</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2691</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>10605</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15411</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -8343,107 +8343,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1479</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4883</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4914</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2,08%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5071</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1479</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5540</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -8456,107 +8456,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2525</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3134</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2792</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>71090</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>71090</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>71090</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>207289</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>191234</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>222004</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>59,8%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>55,17%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>64,04%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>291</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>204235</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>188942</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>219907</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>188165</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>218602</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>59,19%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>54,76%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>63,73%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>207289</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>192035</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>221772</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>59,8%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>390803</t>
+          <t>390091</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>434316</t>
+          <t>432677</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,55%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>105251</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>91543</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>119165</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>30,36%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>26,41%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>34,38%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>106153</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>91155</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>121751</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>92311</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>121135</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>30,76%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>35,28%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>105251</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>91284</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>120261</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>191305</t>
+          <t>190845</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>231753</t>
+          <t>232492</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>27882</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>19898</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>37726</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>29063</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>21560</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>38650</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>21023</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>39546</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>8,42%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>27882</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>20120</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>36633</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46098</t>
+          <t>45542</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>70166</t>
+          <t>69173</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -9030,67 +9030,67 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>3733</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8173</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>3606</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>8043</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>7604</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3733</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>8123</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>12794</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -9138,72 +9138,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5770</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5620</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5479</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>2490</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>6121</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>346644</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>346644</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>346644</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>345054</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>345054</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>345054</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>346644</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>346644</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>346644</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
